--- a/BVSimulationFiles/70.xlsx
+++ b/BVSimulationFiles/70.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0002666666666666666</v>
+        <v>0.0005333333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002727705953278504</v>
+        <v>0.0005455411906557008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002787356216322483</v>
+        <v>0.0005574712432644966</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002845638231377284</v>
+        <v>0.0005691276462754568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002902572505651558</v>
+        <v>0.0005805145011303116</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0002958179281198497</v>
+        <v>0.0005916358562396994</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003012478538093643</v>
+        <v>0.0006024957076187286</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003065489997576331</v>
+        <v>0.0006130979995152662</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003117233125155172</v>
+        <v>0.0006234466250310344</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003167727133677987</v>
+        <v>0.0006335454267355974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003216990986366576</v>
+        <v>0.0006433981972733152</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003265043399816707</v>
+        <v>0.0006530086799633414</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0003311902846963722</v>
+        <v>0.0006623805693927444</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0003357587560014145</v>
+        <v>0.000671517512002829</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003402115533343647</v>
+        <v>0.0006804231066687294</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0003445504526361771</v>
+        <v>0.0006891009052723541</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003487772066343765</v>
+        <v>0.000697554413268753</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003528935451229901</v>
+        <v>0.0007057870902459802</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003569011752392628</v>
+        <v>0.0007138023504785256</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003608017817371938</v>
+        <v>0.0007216035634743876</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0002666666666666666</v>
+        <v>0.0005333333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002727705953278504</v>
+        <v>0.0005455411906557008</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002787356216322483</v>
+        <v>0.0005574712432644966</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002845638231377284</v>
+        <v>0.0005691276462754568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002902572505651558</v>
+        <v>0.0005805145011303116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002958179281198497</v>
+        <v>0.0005916358562396994</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0003012478538093643</v>
+        <v>0.0006024957076187286</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003065489997576331</v>
+        <v>0.0006130979995152662</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003117233125155172</v>
+        <v>0.0006234466250310344</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003167727133677987</v>
+        <v>0.0006335454267355974</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003216990986366576</v>
+        <v>0.0006433981972733152</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003265043399816707</v>
+        <v>0.0006530086799633414</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003311902846963722</v>
+        <v>0.0006623805693927444</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003357587560014145</v>
+        <v>0.000671517512002829</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003402115533343647</v>
+        <v>0.0006804231066687294</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0003445504526361771</v>
+        <v>0.0006891009052723541</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003487772066343765</v>
+        <v>0.000697554413268753</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003528935451229901</v>
+        <v>0.0007057870902459802</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0003569011752392628</v>
+        <v>0.0007138023504785256</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003608017817371938</v>
+        <v>0.0007216035634743876</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/70.xlsx
+++ b/BVSimulationFiles/70.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005333333333333333</v>
+        <v>0.005333333333333332</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005455411906557008</v>
+        <v>0.005455411906557009</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005574712432644966</v>
+        <v>0.005574712432644966</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005691276462754568</v>
+        <v>0.005691276462754568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005805145011303116</v>
+        <v>0.005805145011303116</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005916358562396994</v>
+        <v>0.005916358562396994</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0006024957076187286</v>
+        <v>0.006024957076187286</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006130979995152662</v>
+        <v>0.006130979995152662</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0006234466250310344</v>
+        <v>0.006234466250310344</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006335454267355974</v>
+        <v>0.006335454267355974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006433981972733152</v>
+        <v>0.006433981972733152</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0006530086799633414</v>
+        <v>0.006530086799633414</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0006623805693927444</v>
+        <v>0.006623805693927444</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000671517512002829</v>
+        <v>0.00671517512002829</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0006804231066687294</v>
+        <v>0.006804231066687294</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0006891009052723541</v>
+        <v>0.006891009052723542</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000697554413268753</v>
+        <v>0.00697554413268753</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007057870902459802</v>
+        <v>0.007057870902459802</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007138023504785256</v>
+        <v>0.007138023504785256</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007216035634743876</v>
+        <v>0.007216035634743876</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005333333333333333</v>
+        <v>0.005333333333333332</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005455411906557008</v>
+        <v>0.005455411906557009</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005574712432644966</v>
+        <v>0.005574712432644966</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005691276462754568</v>
+        <v>0.005691276462754568</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005805145011303116</v>
+        <v>0.005805145011303116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005916358562396994</v>
+        <v>0.005916358562396994</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006024957076187286</v>
+        <v>0.006024957076187286</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006130979995152662</v>
+        <v>0.006130979995152662</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006234466250310344</v>
+        <v>0.006234466250310344</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006335454267355974</v>
+        <v>0.006335454267355974</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006433981972733152</v>
+        <v>0.006433981972733152</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006530086799633414</v>
+        <v>0.006530086799633414</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0006623805693927444</v>
+        <v>0.006623805693927444</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000671517512002829</v>
+        <v>0.00671517512002829</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0006804231066687294</v>
+        <v>0.006804231066687294</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0006891009052723541</v>
+        <v>0.006891009052723542</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000697554413268753</v>
+        <v>0.00697554413268753</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007057870902459802</v>
+        <v>0.007057870902459802</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007138023504785256</v>
+        <v>0.007138023504785256</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007216035634743876</v>
+        <v>0.007216035634743876</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/70.xlsx
+++ b/BVSimulationFiles/70.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.005333333333333332</v>
+        <v>0.02263536968418067</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005455411906557009</v>
+        <v>0.02293505723878357</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005574712432644966</v>
+        <v>0.02321550674614816</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005691276462754568</v>
+        <v>0.0234773350637827</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005805145011303116</v>
+        <v>0.02372114266557473</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005916358562396994</v>
+        <v>0.02394751403959177</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006024957076187286</v>
+        <v>0.02415701807671913</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006130979995152662</v>
+        <v>0.02435020845033867</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006234466250310344</v>
+        <v>0.02452762398724795</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006335454267355974</v>
+        <v>0.02468978903001484</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006433981972733152</v>
+        <v>0.02483721379095851</v>
       </c>
       <c r="M2" t="n">
-        <v>0.006530086799633414</v>
+        <v>0.02497039469794347</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006623805693927444</v>
+        <v>0.02508981473216929</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00671517512002829</v>
+        <v>0.02519594375813478</v>
       </c>
       <c r="P2" t="n">
-        <v>0.006804231066687294</v>
+        <v>0.02528923884595125</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.006891009052723542</v>
+        <v>0.02537014458617605</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00697554413268753</v>
+        <v>0.02543909339733347</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007057870902459802</v>
+        <v>0.02549650582628679</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007138023504785256</v>
+        <v>0.02554279084162124</v>
       </c>
       <c r="U2" t="n">
-        <v>0.007216035634743876</v>
+        <v>0.02557834612019489</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.005333333333333332</v>
+        <v>0.02263536968418067</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005455411906557009</v>
+        <v>0.02293505723878357</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005574712432644966</v>
+        <v>0.02321550674614816</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005691276462754568</v>
+        <v>0.0234773350637827</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005805145011303116</v>
+        <v>0.02372114266557473</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005916358562396994</v>
+        <v>0.02394751403959177</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006024957076187286</v>
+        <v>0.02415701807671913</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006130979995152662</v>
+        <v>0.02435020845033867</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006234466250310344</v>
+        <v>0.02452762398724795</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006335454267355974</v>
+        <v>0.02468978903001484</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006433981972733152</v>
+        <v>0.02483721379095851</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006530086799633414</v>
+        <v>0.02497039469794347</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006623805693927444</v>
+        <v>0.02508981473216929</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00671517512002829</v>
+        <v>0.02519594375813478</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006804231066687294</v>
+        <v>0.02528923884595125</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006891009052723542</v>
+        <v>0.02537014458617605</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00697554413268753</v>
+        <v>0.02543909339733347</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007057870902459802</v>
+        <v>0.02549650582628679</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007138023504785256</v>
+        <v>0.02554279084162124</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007216035634743876</v>
+        <v>0.02557834612019489</v>
       </c>
     </row>
   </sheetData>
